--- a/data/trans_orig/Q24A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fuman al día</t>
+          <t>Número medio de cigarrillos que fuman al día (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,35; 18,55</t>
+          <t>15,38; 18,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 19,63</t>
+          <t>15,87; 19,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 15,73</t>
+          <t>12,31; 15,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 16,06</t>
+          <t>11,21; 16,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,17</t>
+          <t>11,67; 15,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,08</t>
+          <t>11,22; 14,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,34</t>
+          <t>9,2; 12,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,13</t>
+          <t>8,99; 11,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,79</t>
+          <t>14,32; 16,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,8</t>
+          <t>14,32; 16,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 13,9</t>
+          <t>11,34; 13,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,51</t>
+          <t>10,52; 13,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,95</t>
+          <t>16,25; 19,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,07; 18,37</t>
+          <t>14,92; 18,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 15,16</t>
+          <t>12,92; 15,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 12,91</t>
+          <t>9,05; 12,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,68</t>
+          <t>11,82; 14,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 15,84</t>
+          <t>13,14; 15,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 11,97</t>
+          <t>9,75; 12,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,88</t>
+          <t>6,9; 8,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,86; 17,0</t>
+          <t>14,94; 16,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 16,82</t>
+          <t>14,52; 16,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 13,62</t>
+          <t>11,98; 13,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,73</t>
+          <t>8,53; 10,75</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 17,05</t>
+          <t>14,62; 17,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 17,63</t>
+          <t>14,57; 17,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 14,26</t>
+          <t>11,38; 14,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 18,42</t>
+          <t>13,21; 17,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,03</t>
+          <t>9,23; 12,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,91</t>
+          <t>11,12; 14,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,38</t>
+          <t>9,25; 12,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 10,6</t>
+          <t>8,2; 10,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 15,03</t>
+          <t>12,92; 15,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,97</t>
+          <t>13,38; 15,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,84</t>
+          <t>10,75; 12,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 14,29</t>
+          <t>11,24; 14,08</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 16,21</t>
+          <t>13,9; 16,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,06; 19,55</t>
+          <t>15,03; 19,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,5</t>
+          <t>12,78; 15,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,55</t>
+          <t>10,09; 14,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 15,5</t>
+          <t>12,14; 15,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,9</t>
+          <t>11,35; 14,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,46</t>
+          <t>8,39; 11,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,66</t>
+          <t>7,46; 10,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,48</t>
+          <t>13,45; 15,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,75</t>
+          <t>13,87; 16,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,24</t>
+          <t>11,14; 13,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,33; 12,21</t>
+          <t>9,21; 12,01</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 21,87</t>
+          <t>16,03; 22,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 18,66</t>
+          <t>14,39; 18,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,89; 17,29</t>
+          <t>12,88; 17,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 17,77</t>
+          <t>14,6; 18,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,44</t>
+          <t>9,59; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,08</t>
+          <t>9,29; 13,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,92; 13,72</t>
+          <t>9,97; 13,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 14,48</t>
+          <t>11,56; 14,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 18,04</t>
+          <t>13,92; 17,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,63; 15,7</t>
+          <t>12,68; 15,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 15,19</t>
+          <t>12,17; 15,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 15,7</t>
+          <t>13,47; 15,97</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,88; 16,93</t>
+          <t>14,86; 17,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,31</t>
+          <t>11,32; 15,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 16,52</t>
+          <t>12,91; 16,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,74</t>
+          <t>12,83; 16,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,83</t>
+          <t>10,5; 13,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,87</t>
+          <t>9,21; 12,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,09</t>
+          <t>7,27; 10,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,63</t>
+          <t>7,14; 9,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,72; 15,67</t>
+          <t>13,74; 15,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,73</t>
+          <t>11,0; 13,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 13,26</t>
+          <t>10,66; 13,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 13,38</t>
+          <t>10,91; 13,43</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,11; 17,25</t>
+          <t>15,12; 17,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 15,4</t>
+          <t>13,25; 15,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,15; 15,83</t>
+          <t>13,22; 15,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,59; 14,03</t>
+          <t>10,57; 13,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,12; 15,06</t>
+          <t>12,13; 15,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 13,42</t>
+          <t>11,07; 13,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,64</t>
+          <t>11,21; 13,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 10,25</t>
+          <t>8,43; 10,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,22; 15,97</t>
+          <t>14,15; 15,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,64; 14,16</t>
+          <t>12,65; 14,18</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 14,43</t>
+          <t>12,59; 14,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 11,83</t>
+          <t>9,82; 11,79</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,9; 19,65</t>
+          <t>16,96; 19,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,11; 18,46</t>
+          <t>16,1; 18,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,99; 15,47</t>
+          <t>12,97; 15,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,14; 17,23</t>
+          <t>15,13; 17,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,13; 13,68</t>
+          <t>11,12; 13,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 13,5</t>
+          <t>11,4; 13,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,33</t>
+          <t>10,25; 12,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,39; 12,38</t>
+          <t>10,4; 12,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,03; 17,11</t>
+          <t>15,07; 17,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,51; 16,24</t>
+          <t>14,41; 16,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,62</t>
+          <t>12,03; 13,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,55; 15,08</t>
+          <t>13,46; 15,08</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,36</t>
+          <t>16,3; 17,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,67</t>
+          <t>15,56; 16,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,64</t>
+          <t>13,61; 14,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,96; 14,33</t>
+          <t>12,89; 14,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,19</t>
+          <t>12,1; 13,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,16</t>
+          <t>12,06; 13,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,44</t>
+          <t>10,49; 11,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,01</t>
+          <t>9,11; 10,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 15,66</t>
+          <t>14,82; 15,64</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,22; 15,01</t>
+          <t>14,24; 15,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,35; 13,11</t>
+          <t>12,37; 13,13</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,29</t>
+          <t>11,37; 12,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,56</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>12,17</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,38; 18,62</t>
+          <t>15,48; 18,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,56</t>
+          <t>15,8; 19,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 15,71</t>
+          <t>12,29; 15,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 16,02</t>
+          <t>11,85; 16,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,24</t>
+          <t>11,53; 15,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 14,21</t>
+          <t>11,29; 14,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,34</t>
+          <t>9,39; 12,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 11,23</t>
+          <t>9,04; 11,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 16,92</t>
+          <t>14,32; 16,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 16,89</t>
+          <t>14,25; 17,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 13,84</t>
+          <t>11,45; 13,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 13,47</t>
+          <t>11,02; 13,64</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 19,09</t>
+          <t>16,23; 19,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 18,17</t>
+          <t>15,01; 18,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 15,12</t>
+          <t>12,97; 15,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 12,98</t>
+          <t>9,09; 12,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 14,59</t>
+          <t>12,1; 14,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 15,87</t>
+          <t>13,03; 16,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,05</t>
+          <t>9,75; 12,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,89</t>
+          <t>7,02; 9,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 16,88</t>
+          <t>14,96; 17,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,52; 16,78</t>
+          <t>14,53; 16,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,98; 13,58</t>
+          <t>11,93; 13,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,75</t>
+          <t>8,47; 10,87</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,47</t>
+          <t>15,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,39</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>12,5</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 17,07</t>
+          <t>14,73; 17,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 17,62</t>
+          <t>14,61; 17,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 14,7</t>
+          <t>11,22; 14,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 17,83</t>
+          <t>12,96; 17,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 12,08</t>
+          <t>9,12; 12,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,12; 14,77</t>
+          <t>11,14; 14,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 12,28</t>
+          <t>9,28; 12,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 10,62</t>
+          <t>8,33; 10,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 15,11</t>
+          <t>12,92; 14,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,83</t>
+          <t>13,54; 15,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,92</t>
+          <t>10,71; 12,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,08</t>
+          <t>11,19; 14,11</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,39</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>10,85</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 16,29</t>
+          <t>13,84; 16,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 19,53</t>
+          <t>14,96; 19,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,7</t>
+          <t>12,72; 15,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 14,73</t>
+          <t>10,53; 14,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,31</t>
+          <t>12,17; 15,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 14,83</t>
+          <t>11,3; 14,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 11,37</t>
+          <t>8,47; 11,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,55</t>
+          <t>7,51; 10,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 15,43</t>
+          <t>13,5; 15,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 16,69</t>
+          <t>13,83; 16,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 13,33</t>
+          <t>11,3; 13,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 12,01</t>
+          <t>9,38; 12,2</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>16,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,03</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,63</t>
+          <t>14,91</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,03; 22,0</t>
+          <t>16,19; 21,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,39; 18,47</t>
+          <t>14,62; 18,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 17,18</t>
+          <t>12,89; 17,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,6; 18,16</t>
+          <t>14,98; 17,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,65</t>
+          <t>9,53; 13,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,02</t>
+          <t>9,13; 13,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 13,75</t>
+          <t>10,12; 14,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,83</t>
+          <t>11,45; 14,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 17,75</t>
+          <t>14,1; 17,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 15,71</t>
+          <t>12,73; 15,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 15,29</t>
+          <t>12,16; 15,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 15,97</t>
+          <t>13,87; 15,99</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>12,32</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,86; 17,01</t>
+          <t>14,94; 16,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 15,39</t>
+          <t>11,48; 15,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 16,39</t>
+          <t>13,16; 16,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,83; 16,46</t>
+          <t>13,33; 17,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,91</t>
+          <t>10,47; 13,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 12,68</t>
+          <t>9,34; 12,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,0</t>
+          <t>7,2; 9,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,45</t>
+          <t>7,01; 9,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,74; 15,67</t>
+          <t>13,71; 15,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,77</t>
+          <t>10,87; 13,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 13,18</t>
+          <t>10,7; 13,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,43</t>
+          <t>11,15; 14,03</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>10,68</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,12; 17,26</t>
+          <t>15,06; 17,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 15,3</t>
+          <t>13,24; 15,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 15,89</t>
+          <t>13,24; 15,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,57; 13,95</t>
+          <t>10,46; 13,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,13; 15,05</t>
+          <t>12,14; 15,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,07; 13,53</t>
+          <t>11,06; 13,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,71</t>
+          <t>11,2; 13,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,43; 10,16</t>
+          <t>8,42; 10,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,15; 15,89</t>
+          <t>14,19; 15,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 14,18</t>
+          <t>12,68; 14,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,59; 14,41</t>
+          <t>12,61; 14,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 11,79</t>
+          <t>9,82; 11,72</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,21</t>
+          <t>16,23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>11,34</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>14,31</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,96; 19,69</t>
+          <t>16,98; 19,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,49</t>
+          <t>16,02; 18,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 15,51</t>
+          <t>13,06; 15,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 17,23</t>
+          <t>15,19; 17,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,12; 13,6</t>
+          <t>11,09; 13,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,44</t>
+          <t>11,41; 13,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 12,25</t>
+          <t>10,33; 12,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,4; 12,46</t>
+          <t>10,36; 12,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,07; 17,02</t>
+          <t>15,06; 17,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,41; 16,04</t>
+          <t>14,43; 16,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,03; 13,71</t>
+          <t>12,02; 13,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,46; 15,08</t>
+          <t>13,55; 15,13</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>11,93</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,36</t>
+          <t>16,36; 17,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,69</t>
+          <t>15,56; 16,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,61; 14,66</t>
+          <t>13,63; 14,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,89; 14,31</t>
+          <t>13,09; 14,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,1; 13,22</t>
+          <t>12,08; 13,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,1</t>
+          <t>12,04; 13,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 11,44</t>
+          <t>10,53; 11,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,02</t>
+          <t>9,21; 10,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,82; 15,64</t>
+          <t>14,88; 15,66</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14,24; 15,05</t>
+          <t>14,22; 15,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,37; 13,13</t>
+          <t>12,35; 13,09</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,27</t>
+          <t>11,52; 12,35</t>
         </is>
       </c>
     </row>
